--- a/tools/_out/orfs_gen_20261020/out/DesignTable_FS6504C_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/DesignTable_FS6504C_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG5"/>
+  <dimension ref="A1:BF5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,160 +549,155 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>FSWB_CSANG@DRIVE</t>
+          <t>FSWB_MINR@DRIVE</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>FSWB_MINR@DRIVE</t>
+          <t>FSWB_THDL@DRIVE</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>FSWB_THDL@DRIVE</t>
+          <t>FSWB_RELANG@DRIVE</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>FSWB_RELANG@DRIVE</t>
+          <t>FSWB_RELR@DRIVE</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>FSWB_RELR@DRIVE</t>
+          <t>FSWB_STEMR@DRIVE</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>FSWB_STEMR@DRIVE</t>
+          <t>FSWB_HEADL@DRIVE</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>FSWB_HEADL@DRIVE</t>
+          <t>HELIXDIA@HELIXSK_B</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>HELIXDIA@HELIXSK_B</t>
+          <t>HEIGHT@HELIX_B</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>HEIGHT@HELIX_B</t>
+          <t>PITCH@HELIX_B</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>PITCH@HELIX_B</t>
+          <t>PROF_R@THDPROF_B</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>PROF_R@THDPROF_B</t>
+          <t>APEXR@THDPROF_B</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>APEXR@THDPROF_B</t>
+          <t>FSWB_CBR@DRIVE</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>FSWB_CBR@DRIVE</t>
+          <t>FSWB_CBD@DRIVE</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>FSWB_CBD@DRIVE</t>
+          <t>PROF_AX@THDPROF_B</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>PROF_AX@THDPROF_B</t>
+          <t>DA@BORE_A</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>DA@BORE_A</t>
+          <t>DEPTH@BORECUT_A</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>DEPTH@BORECUT_A</t>
+          <t>DB@BORE_B</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>DB@BORE_B</t>
+          <t>DEPTH@BORECUT_B</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>DEPTH@BORECUT_B</t>
+          <t>START@BORECUT_B</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>START@BORECUT_B</t>
+          <t>DEPTH@HEXCUT</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>DEPTH@HEXCUT</t>
+          <t>NUTHEX@NUTHEX</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>NUTHEX@NUTHEX</t>
+          <t>DEPTH@NUTCUT</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>DEPTH@NUTCUT</t>
+          <t>$PRP@PartNo</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>$PRP@PartNo</t>
+          <t>$PRP@Description</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>$PRP@Description</t>
+          <t>$PRP@GeometryRoot</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>$PRP@GeometryRoot</t>
+          <t>$PRP@EndA_Thread</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>$PRP@EndA_Thread</t>
+          <t>$PRP@EndB_Thread</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>$PRP@EndB_Thread</t>
+          <t>$PRP@DataStatus</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>$PRP@DataStatus</t>
+          <t>$PRP@AxialSource</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>$PRP@AxialSource</t>
+          <t>$COMMENT</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
-        <is>
-          <t>$COMMENT</t>
-        </is>
-      </c>
-      <c r="BG1" t="inlineStr">
         <is>
           <t>$PRP@OMiSKU</t>
         </is>
@@ -793,115 +788,112 @@
         <v>0.532</v>
       </c>
       <c r="AB2" t="n">
-        <v>60</v>
+        <v>0.46134</v>
       </c>
       <c r="AC2" t="n">
+        <v>0.42121</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>45</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.4615</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.9226799999999999</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AK2" t="n">
         <v>0.46134</v>
       </c>
-      <c r="AD2" t="n">
-        <v>0.40591</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>45</v>
-      </c>
-      <c r="AF2" t="n">
+      <c r="AL2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AM2" t="n">
         <v>0.51</v>
       </c>
-      <c r="AG2" t="n">
-        <v>0.4615</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0.236</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.9226799999999999</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.484</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.07142999999999999</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0.46134</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AN2" t="n">
-        <v>0.51</v>
+        <v>0.05</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.05</v>
+        <v>2.732</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.732</v>
+        <v>0.45</v>
       </c>
       <c r="AQ2" t="n">
+        <v>1.009</v>
+      </c>
+      <c r="AR2" t="n">
         <v>0.45</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AS2" t="n">
+        <v>1.211</v>
+      </c>
+      <c r="AT2" t="n">
         <v>1.009</v>
       </c>
-      <c r="AS2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.211</v>
-      </c>
       <c r="AU2" t="n">
-        <v>1.009</v>
+        <v>1.26</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AX2" t="n">
         <v>0.548</v>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>FS6504-10-10</t>
+        </is>
+      </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>FS6504-10-10</t>
+          <t>ORFS Swivel Union (female face-seal swivel x male JIC) - swivel nut mouth counterbored (-10 up), 7/8-14 x 1-14 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>ORFS Swivel Union (female face-seal swivel x male JIC) - swivel nut mouth counterbored (-10 up), 7/8-14 x 1-14 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>FS6504C</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>FS6504C</t>
+          <t>7/8-14</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>7/8-14</t>
+          <t>1-14 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>1-14 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>Air-Way FF7504 (s19, double-pass 2026-10-15, parts.air-way.com/api/series/19, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p6 FS6504-10-10 (ORFS-p006-t03) | MODEL: L40 JIC tip -&gt; seal face, L38 hex JIC-side face -&gt; seal face, L39 hex length (check), body hex C2, bores D2 (JIC side) / D19 (swivel): review table (Air-Way, staged FS table; OMi website list decides the parts); the row length runs to the stem seal face (Brennan FS6565-08-08: Air-Way L45 2.12 = seal face to seal face); the model length (LNUT, nut face to the JIC tip) = L40 + the measured seal -&gt; nut face distance SEAL of the swivel; body hex = Air-Way L39 (its swivel-side face L38 - L39 before the seal face; Brennan's measured swivel body face in $COMMENT); male JIC end MS33656J (2403 table, VERIFIED vs Brennan; = Air-Way L40 - L38 at every size); Air-Way S on FF7504 is not a nut hex (PLAN D3): the nut = FF318 S (Q-FS-NUT); bore step at the body-hex mid-plane (ASSUMPTION, as 6504); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan)</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>Air-Way FF7504 (s19, double-pass 2026-10-15, parts.air-way.com/api/series/19, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p6 FS6504-10-10 (ORFS-p006-t03) | MODEL: L40 JIC tip -&gt; seal face, L38 hex JIC-side face -&gt; seal face, L39 hex length (check), body hex C2, bores D2 (JIC side) / D19 (swivel): review table (Air-Way, staged FS table; OMi website list decides the parts); the row length runs to the stem seal face (Brennan FS6565-08-08: Air-Way L45 2.12 = seal face to seal face); the model length (LNUT, nut face to the JIC tip) = L40 + the measured seal -&gt; nut face distance SEAL of the swivel; body hex = Air-Way L39 (its swivel-side face L38 - L39 before the seal face; Brennan's measured swivel body face in $COMMENT); male JIC end MS33656J (2403 table, VERIFIED vs Brennan; = Air-Way L40 - L38 at every size); Air-Way S on FF7504 is not a nut hex (PLAN D3): the nut = FF318 S (Q-FS-NUT); bore step at the body-hex mid-plane (ASSUMPTION, as 6504); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan)</t>
+          <t>Air-Way FF7504 (built to Air-Way); Brennan p6 DIFFERS (up to 0.048 in): overall length L40=2.20 vs Brennan L LGTH=2.248 | OMi FS6504 (FFSS x MJ) = Air-Way FF7504 (37 deg male JIC x female ORFS swivel), NOT Air-Way FF6504 (MFS x FFSS union). Air-Way C2 / S do not match Brennan C HEX / H HEX - their meaning needs the Air-Way drawing; hexes not compared | OMi parts file row 5602 (no dimensions) | swivel nut hex SHEX printed 0.82 - not the FF318 nut S 1.13 of -10: built with FF318 S 1.13 (Q-FS-NUT); body hex face -&gt; seal face = Air-Way L38 - L39 0.94 (built); Brennan swivel (FS6500-10-10-FG leg) 0.980 - differ by -0.040 (Air-Way vs Brennan: tell the user)</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
-        <is>
-          <t>Air-Way FF7504 (built to Air-Way); Brennan p6 DIFFERS (up to 0.048 in): overall length L40=2.20 vs Brennan L LGTH=2.248 | OMi FS6504 (FFSS x MJ) = Air-Way FF7504 (37 deg male JIC x female ORFS swivel), NOT Air-Way FF6504 (MFS x FFSS union). Air-Way C2 / S do not match Brennan C HEX / H HEX - their meaning needs the Air-Way drawing; hexes not compared | OMi parts file row 5602 (no dimensions) | swivel nut hex SHEX printed 0.82 - not the FF318 nut S 1.13 of -10: built with FF318 S 1.13 (Q-FS-NUT); body hex face -&gt; seal face = Air-Way L38 - L39 0.94 (built); Brennan swivel (FS6500-10-10-FG leg) 0.980 - differ by -0.040 (Air-Way vs Brennan: tell the user)</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
         <is>
           <t>FS6504-10-10</t>
         </is>
@@ -992,115 +984,112 @@
         <v>0.571</v>
       </c>
       <c r="AB3" t="n">
-        <v>60</v>
+        <v>0.54864</v>
       </c>
       <c r="AC3" t="n">
+        <v>0.45364</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>45</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.5485</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.09728</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.5356</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AK3" t="n">
         <v>0.54864</v>
       </c>
-      <c r="AD3" t="n">
-        <v>0.45364</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>45</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.5485</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0.256</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.09728</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0.5356</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0.08333</v>
-      </c>
       <c r="AL3" t="n">
-        <v>0.54864</v>
+        <v>0.59375</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.59375</v>
+        <v>0.604</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.604</v>
+        <v>0.05</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.05</v>
+        <v>3.071</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.071</v>
+        <v>0.55</v>
       </c>
       <c r="AQ3" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="AR3" t="n">
         <v>0.55</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AS3" t="n">
+        <v>1.353</v>
+      </c>
+      <c r="AT3" t="n">
         <v>1.167</v>
       </c>
-      <c r="AS3" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1.353</v>
-      </c>
       <c r="AU3" t="n">
-        <v>1.167</v>
+        <v>1.47</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AX3" t="n">
         <v>0.599</v>
       </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>FS6504-12-12</t>
+        </is>
+      </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>FS6504-12-12</t>
+          <t>ORFS Swivel Union (female face-seal swivel x male JIC) - swivel nut mouth counterbored (-10 up), 1 1/16-12 x 1 3/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>ORFS Swivel Union (female face-seal swivel x male JIC) - swivel nut mouth counterbored (-10 up), 1 1/16-12 x 1 3/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>FS6504C</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>FS6504C</t>
+          <t>1 1/16-12</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>1 1/16-12</t>
+          <t>1 3/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>1 3/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>Air-Way FF7504 (s19, double-pass 2026-10-15, parts.air-way.com/api/series/19, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p6 FS6504-12-12 (ORFS-p006-t03) | MODEL: L40 JIC tip -&gt; seal face, L38 hex JIC-side face -&gt; seal face, L39 hex length (check), body hex C2, bores D2 (JIC side) / D19 (swivel): review table (Air-Way, staged FS table; OMi website list decides the parts); the row length runs to the stem seal face (Brennan FS6565-08-08: Air-Way L45 2.12 = seal face to seal face); the model length (LNUT, nut face to the JIC tip) = L40 + the measured seal -&gt; nut face distance SEAL of the swivel; body hex = Air-Way L39 (its swivel-side face L38 - L39 before the seal face; Brennan's measured swivel body face in $COMMENT); male JIC end MS33656J (2403 table, VERIFIED vs Brennan; = Air-Way L40 - L38 at every size); Air-Way S on FF7504 is not a nut hex (PLAN D3): the nut = FF318 S (Q-FS-NUT); bore step at the body-hex mid-plane (ASSUMPTION, as 6504); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan)</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>Air-Way FF7504 (s19, double-pass 2026-10-15, parts.air-way.com/api/series/19, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p6 FS6504-12-12 (ORFS-p006-t03) | MODEL: L40 JIC tip -&gt; seal face, L38 hex JIC-side face -&gt; seal face, L39 hex length (check), body hex C2, bores D2 (JIC side) / D19 (swivel): review table (Air-Way, staged FS table; OMi website list decides the parts); the row length runs to the stem seal face (Brennan FS6565-08-08: Air-Way L45 2.12 = seal face to seal face); the model length (LNUT, nut face to the JIC tip) = L40 + the measured seal -&gt; nut face distance SEAL of the swivel; body hex = Air-Way L39 (its swivel-side face L38 - L39 before the seal face; Brennan's measured swivel body face in $COMMENT); male JIC end MS33656J (2403 table, VERIFIED vs Brennan; = Air-Way L40 - L38 at every size); Air-Way S on FF7504 is not a nut hex (PLAN D3): the nut = FF318 S (Q-FS-NUT); bore step at the body-hex mid-plane (ASSUMPTION, as 6504); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan)</t>
+          <t>Air-Way FF7504 = Brennan p6 on overall length (rounding-only differences count as equal) | only the overall length L40 is compared: Air-Way FF7504 "S" (0.40 ... 1.46) cannot be a nut hex and C2 equals Brennan's H HEX only at -08, so no hex is checked (plan D3, Q-FS-NUT) - ASSUMED, not VERIFIED | OMi FS6504 (FFSS x MJ) = Air-Way FF7504 (37 deg male JIC x female ORFS swivel), NOT Air-Way FF6504 (MFS x FFSS union). Air-Way C2 / S do not match Brennan C HEX / H HEX - their meaning needs the Air-Way drawing; hexes not compared | OMi parts file row 5603 (no dimensions) | swivel nut hex SHEX printed 0.98 - not the FF318 nut S 1.38 of -12: built with FF318 S 1.38 (Q-FS-NUT); body hex face -&gt; seal face = Air-Way L38 - L39 1.03 (built); Brennan swivel (FS6500-12-12-FG leg) 1.120 - differ by -0.090 (Air-Way vs Brennan: tell the user)</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
-        <is>
-          <t>Air-Way FF7504 = Brennan p6 on overall length (rounding-only differences count as equal) | only the overall length L40 is compared: Air-Way FF7504 "S" (0.40 ... 1.46) cannot be a nut hex and C2 equals Brennan's H HEX only at -08, so no hex is checked (plan D3, Q-FS-NUT) - ASSUMED, not VERIFIED | OMi FS6504 (FFSS x MJ) = Air-Way FF7504 (37 deg male JIC x female ORFS swivel), NOT Air-Way FF6504 (MFS x FFSS union). Air-Way C2 / S do not match Brennan C HEX / H HEX - their meaning needs the Air-Way drawing; hexes not compared | OMi parts file row 5603 (no dimensions) | swivel nut hex SHEX printed 0.98 - not the FF318 nut S 1.38 of -12: built with FF318 S 1.38 (Q-FS-NUT); body hex face -&gt; seal face = Air-Way L38 - L39 1.03 (built); Brennan swivel (FS6500-12-12-FG leg) 1.120 - differ by -0.090 (Air-Way vs Brennan: tell the user)</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
         <is>
           <t>FS6504-12-12</t>
         </is>
@@ -1191,115 +1180,112 @@
         <v>0.583</v>
       </c>
       <c r="AB4" t="n">
-        <v>60</v>
+        <v>0.67364</v>
       </c>
       <c r="AC4" t="n">
+        <v>0.46574</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>45</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.6735</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.34728</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.5477</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AK4" t="n">
         <v>0.67364</v>
       </c>
-      <c r="AD4" t="n">
-        <v>0.46574</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>45</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.6735</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.276</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.34728</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0.5477</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0.08333</v>
-      </c>
       <c r="AL4" t="n">
-        <v>0.67364</v>
+        <v>0.71875</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.71875</v>
+        <v>0.729</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.729</v>
+        <v>0.05</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.05</v>
+        <v>3.243</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.243</v>
+        <v>0.79</v>
       </c>
       <c r="AQ4" t="n">
+        <v>1.2305</v>
+      </c>
+      <c r="AR4" t="n">
         <v>0.79</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="AS4" t="n">
+        <v>1.4495</v>
+      </c>
+      <c r="AT4" t="n">
         <v>1.2305</v>
       </c>
-      <c r="AS4" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.4495</v>
-      </c>
       <c r="AU4" t="n">
-        <v>1.2305</v>
+        <v>1.55</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AX4" t="n">
         <v>0.65</v>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>FS6504-16-16</t>
+        </is>
+      </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>FS6504-16-16</t>
+          <t>ORFS Swivel Union (female face-seal swivel x male JIC) - swivel nut mouth counterbored (-10 up), 1 5/16-12 x 1 7/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>ORFS Swivel Union (female face-seal swivel x male JIC) - swivel nut mouth counterbored (-10 up), 1 5/16-12 x 1 7/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>FS6504C</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>FS6504C</t>
+          <t>1 5/16-12</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>1 5/16-12</t>
+          <t>1 7/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>1 7/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>Air-Way FF7504 (s19, double-pass 2026-10-15, parts.air-way.com/api/series/19, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p6 FS6504-16-16 (ORFS-p006-t03) | MODEL: L40 JIC tip -&gt; seal face, L38 hex JIC-side face -&gt; seal face, L39 hex length (check), body hex C2, bores D2 (JIC side) / D19 (swivel): review table (Air-Way, staged FS table; OMi website list decides the parts); the row length runs to the stem seal face (Brennan FS6565-08-08: Air-Way L45 2.12 = seal face to seal face); the model length (LNUT, nut face to the JIC tip) = L40 + the measured seal -&gt; nut face distance SEAL of the swivel; body hex = Air-Way L39 (its swivel-side face L38 - L39 before the seal face; Brennan's measured swivel body face in $COMMENT); male JIC end MS33656J (2403 table, VERIFIED vs Brennan; = Air-Way L40 - L38 at every size); Air-Way S on FF7504 is not a nut hex (PLAN D3): the nut = FF318 S (Q-FS-NUT); bore step at the body-hex mid-plane (ASSUMPTION, as 6504); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan)</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>Air-Way FF7504 (s19, double-pass 2026-10-15, parts.air-way.com/api/series/19, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p6 FS6504-16-16 (ORFS-p006-t03) | MODEL: L40 JIC tip -&gt; seal face, L38 hex JIC-side face -&gt; seal face, L39 hex length (check), body hex C2, bores D2 (JIC side) / D19 (swivel): review table (Air-Way, staged FS table; OMi website list decides the parts); the row length runs to the stem seal face (Brennan FS6565-08-08: Air-Way L45 2.12 = seal face to seal face); the model length (LNUT, nut face to the JIC tip) = L40 + the measured seal -&gt; nut face distance SEAL of the swivel; body hex = Air-Way L39 (its swivel-side face L38 - L39 before the seal face; Brennan's measured swivel body face in $COMMENT); male JIC end MS33656J (2403 table, VERIFIED vs Brennan; = Air-Way L40 - L38 at every size); Air-Way S on FF7504 is not a nut hex (PLAN D3): the nut = FF318 S (Q-FS-NUT); bore step at the body-hex mid-plane (ASSUMPTION, as 6504); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan)</t>
+          <t>Air-Way FF7504 (built to Air-Way); Brennan p6 DIFFERS (&lt;= 0.02 in): overall length L40=2.66 vs Brennan L LGTH=2.650 | OMi FS6504 (FFSS x MJ) = Air-Way FF7504 (37 deg male JIC x female ORFS swivel), NOT Air-Way FF6504 (MFS x FFSS union). Air-Way C2 / S do not match Brennan C HEX / H HEX - their meaning needs the Air-Way drawing; hexes not compared | OMi parts file row 5604 (no dimensions) | swivel nut hex SHEX printed 1.16 - not the FF318 nut S 1.63 of -16: built with FF318 S 1.63 (Q-FS-NUT); body hex face -&gt; seal face = Air-Way L38 - L39 1.11 (built); Brennan swivel (FS6500-16-16-FG leg) 1.200 - differ by -0.090 (Air-Way vs Brennan: tell the user)</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
-        <is>
-          <t>Air-Way FF7504 (built to Air-Way); Brennan p6 DIFFERS (&lt;= 0.02 in): overall length L40=2.66 vs Brennan L LGTH=2.650 | OMi FS6504 (FFSS x MJ) = Air-Way FF7504 (37 deg male JIC x female ORFS swivel), NOT Air-Way FF6504 (MFS x FFSS union). Air-Way C2 / S do not match Brennan C HEX / H HEX - their meaning needs the Air-Way drawing; hexes not compared | OMi parts file row 5604 (no dimensions) | swivel nut hex SHEX printed 1.16 - not the FF318 nut S 1.63 of -16: built with FF318 S 1.63 (Q-FS-NUT); body hex face -&gt; seal face = Air-Way L38 - L39 1.11 (built); Brennan swivel (FS6500-16-16-FG leg) 1.200 - differ by -0.090 (Air-Way vs Brennan: tell the user)</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
         <is>
           <t>FS6504-16-16</t>
         </is>
@@ -1390,115 +1376,112 @@
         <v>0.583</v>
       </c>
       <c r="AB5" t="n">
-        <v>60</v>
+        <v>0.79864</v>
       </c>
       <c r="AC5" t="n">
+        <v>0.45564</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>45</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.7985</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.59728</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.5376</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AK5" t="n">
         <v>0.79864</v>
       </c>
-      <c r="AD5" t="n">
-        <v>0.45564</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>45</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0.7985</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0.276</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.59728</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0.5376</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0.08333</v>
-      </c>
       <c r="AL5" t="n">
-        <v>0.79864</v>
+        <v>0.84375</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.84375</v>
+        <v>0.854</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.854</v>
+        <v>0.05</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.05</v>
+        <v>3.383</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.383</v>
+        <v>1.02</v>
       </c>
       <c r="AQ5" t="n">
+        <v>1.304</v>
+      </c>
+      <c r="AR5" t="n">
         <v>1.02</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AS5" t="n">
+        <v>1.516</v>
+      </c>
+      <c r="AT5" t="n">
         <v>1.304</v>
       </c>
-      <c r="AS5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1.516</v>
-      </c>
       <c r="AU5" t="n">
-        <v>1.304</v>
+        <v>1.65</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AX5" t="n">
         <v>0.65</v>
       </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>FS6504-20-20</t>
+        </is>
+      </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>FS6504-20-20</t>
+          <t>ORFS Swivel Union (female face-seal swivel x male JIC) - swivel nut mouth counterbored (-10 up), 1 5/8-12 x 1 11/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>ORFS Swivel Union (female face-seal swivel x male JIC) - swivel nut mouth counterbored (-10 up), 1 5/8-12 x 1 11/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>FS6504C</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>FS6504C</t>
+          <t>1 5/8-12</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>1 5/8-12</t>
+          <t>1 11/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>1 11/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>Air-Way FF7504 (s19, double-pass 2026-10-15, parts.air-way.com/api/series/19, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p6 FS6504-20-20 (ORFS-p006-t03) | MODEL: L40 JIC tip -&gt; seal face, L38 hex JIC-side face -&gt; seal face, L39 hex length (check), body hex C2, bores D2 (JIC side) / D19 (swivel): review table (Air-Way, staged FS table; OMi website list decides the parts); the row length runs to the stem seal face (Brennan FS6565-08-08: Air-Way L45 2.12 = seal face to seal face); the model length (LNUT, nut face to the JIC tip) = L40 + the measured seal -&gt; nut face distance SEAL of the swivel; body hex = Air-Way L39 (its swivel-side face L38 - L39 before the seal face; Brennan's measured swivel body face in $COMMENT); male JIC end MS33656J (2403 table, VERIFIED vs Brennan; = Air-Way L40 - L38 at every size); Air-Way S on FF7504 is not a nut hex (PLAN D3): the nut = FF318 S (Q-FS-NUT); bore step at the body-hex mid-plane (ASSUMPTION, as 6504); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan)</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>Air-Way FF7504 (s19, double-pass 2026-10-15, parts.air-way.com/api/series/19, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p6 FS6504-20-20 (ORFS-p006-t03) | MODEL: L40 JIC tip -&gt; seal face, L38 hex JIC-side face -&gt; seal face, L39 hex length (check), body hex C2, bores D2 (JIC side) / D19 (swivel): review table (Air-Way, staged FS table; OMi website list decides the parts); the row length runs to the stem seal face (Brennan FS6565-08-08: Air-Way L45 2.12 = seal face to seal face); the model length (LNUT, nut face to the JIC tip) = L40 + the measured seal -&gt; nut face distance SEAL of the swivel; body hex = Air-Way L39 (its swivel-side face L38 - L39 before the seal face; Brennan's measured swivel body face in $COMMENT); male JIC end MS33656J (2403 table, VERIFIED vs Brennan; = Air-Way L40 - L38 at every size); Air-Way S on FF7504 is not a nut hex (PLAN D3): the nut = FF318 S (Q-FS-NUT); bore step at the body-hex mid-plane (ASSUMPTION, as 6504); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan)</t>
+          <t>Air-Way FF7504 (built to Air-Way); Brennan p6 DIFFERS (up to 0.088 in): overall length L40=2.80 vs Brennan L LGTH=2.888 | OMi FS6504 (FFSS x MJ) = Air-Way FF7504 (37 deg male JIC x female ORFS swivel), NOT Air-Way FF6504 (MFS x FFSS union). Air-Way C2 / S do not match Brennan C HEX / H HEX - their meaning needs the Air-Way drawing; hexes not compared | OMi parts file row 5605 (no dimensions) | swivel nut hex SHEX printed 1.46 - not the FF318 nut S 1.88 of -20: built with FF318 S 1.88 (Q-FS-NUT); body hex face -&gt; seal face = Air-Way L38 - L39 1.15 (built); Brennan swivel (FS6500-20-20-FG leg) 1.200 - differ by -0.050 (Air-Way vs Brennan: tell the user)</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
-        <is>
-          <t>Air-Way FF7504 (built to Air-Way); Brennan p6 DIFFERS (up to 0.088 in): overall length L40=2.80 vs Brennan L LGTH=2.888 | OMi FS6504 (FFSS x MJ) = Air-Way FF7504 (37 deg male JIC x female ORFS swivel), NOT Air-Way FF6504 (MFS x FFSS union). Air-Way C2 / S do not match Brennan C HEX / H HEX - their meaning needs the Air-Way drawing; hexes not compared | OMi parts file row 5605 (no dimensions) | swivel nut hex SHEX printed 1.46 - not the FF318 nut S 1.88 of -20: built with FF318 S 1.88 (Q-FS-NUT); body hex face -&gt; seal face = Air-Way L38 - L39 1.15 (built); Brennan swivel (FS6500-20-20-FG leg) 1.200 - differ by -0.050 (Air-Way vs Brennan: tell the user)</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
         <is>
           <t>FS6504-20-20</t>
         </is>
